--- a/кейс2_каналы_продаж/Кейс2_Анализ_каналов_продаж_заполнено.xlsx
+++ b/кейс2_каналы_продаж/Кейс2_Анализ_каналов_продаж_заполнено.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -491,8 +491,6 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -532,25 +530,15 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ozon </t>
+          <t>Блогер</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>WB</t>
+          <t>канал n</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Блогер</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>канал n</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
@@ -572,19 +560,13 @@
         <v>62000</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>145000</v>
+        <v>85000</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>168000</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>85000</v>
-      </c>
-      <c r="H5" s="5" t="n">
         <v>96000</v>
       </c>
-      <c r="I5" s="6">
-        <f>SUM(B5:H5)</f>
+      <c r="G5" s="6">
+        <f>SUM(B5:F5)</f>
         <v/>
       </c>
     </row>
@@ -604,19 +586,13 @@
         <v>2480</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>5800</v>
+        <v>1700</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>5880</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>1700</v>
-      </c>
-      <c r="H6" s="5" t="n">
         <v>768</v>
       </c>
-      <c r="I6" s="6">
-        <f>SUM(B6:H6)</f>
+      <c r="G6" s="6">
+        <f>SUM(B6:F6)</f>
         <v/>
       </c>
     </row>
@@ -636,19 +612,13 @@
         <v>223</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>522</v>
+        <v>136</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>470</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>136</v>
-      </c>
-      <c r="H7" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="I7" s="6">
-        <f>SUM(B7:H7)</f>
+      <c r="G7" s="6">
+        <f>SUM(B7:F7)</f>
         <v/>
       </c>
     </row>
@@ -668,19 +638,13 @@
         <v>28</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="H8" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I8" s="6">
-        <f>SUM(B8:H8)</f>
+      <c r="G8" s="6">
+        <f>SUM(B8:F8)</f>
         <v/>
       </c>
     </row>
@@ -700,19 +664,13 @@
         <v>33656</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>89694</v>
+        <v>36780</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>72405</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>36780</v>
-      </c>
-      <c r="H9" s="7" t="n">
         <v>6513</v>
       </c>
-      <c r="I9" s="8">
-        <f>SUM(B9:H9)</f>
+      <c r="G9" s="8">
+        <f>SUM(B9:F9)</f>
         <v/>
       </c>
     </row>
@@ -732,19 +690,13 @@
         <v>18000</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>26000</v>
+        <v>35000</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>30000</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>35000</v>
-      </c>
-      <c r="H10" s="7" t="n">
         <v>22000</v>
       </c>
-      <c r="I10" s="8">
-        <f>SUM(B10:H10)</f>
+      <c r="G10" s="8">
+        <f>SUM(B10:F10)</f>
         <v/>
       </c>
     </row>
@@ -774,16 +726,8 @@
         <f>F10/F6</f>
         <v/>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="10">
         <f>G10/G6</f>
-        <v/>
-      </c>
-      <c r="H11" s="9">
-        <f>H10/H6</f>
-        <v/>
-      </c>
-      <c r="I11" s="10">
-        <f>I10/I6</f>
         <v/>
       </c>
     </row>
@@ -813,16 +757,8 @@
         <f>F10/F8</f>
         <v/>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="12">
         <f>G10/G8</f>
-        <v/>
-      </c>
-      <c r="H12" s="11">
-        <f>H10/H8</f>
-        <v/>
-      </c>
-      <c r="I12" s="12">
-        <f>I10/I8</f>
         <v/>
       </c>
     </row>
@@ -852,16 +788,8 @@
         <f>F9-F10</f>
         <v/>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="12">
         <f>G9-G10</f>
-        <v/>
-      </c>
-      <c r="H13" s="11">
-        <f>H9-H10</f>
-        <v/>
-      </c>
-      <c r="I13" s="12">
-        <f>I9-I10</f>
         <v/>
       </c>
     </row>
@@ -891,16 +819,8 @@
         <f>F9/F10</f>
         <v/>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="14">
         <f>G9/G10</f>
-        <v/>
-      </c>
-      <c r="H14" s="13">
-        <f>H9/H10</f>
-        <v/>
-      </c>
-      <c r="I14" s="14">
-        <f>I9/I10</f>
         <v/>
       </c>
     </row>
@@ -930,16 +850,8 @@
         <f>F6/F5</f>
         <v/>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="16">
         <f>G6/G5</f>
-        <v/>
-      </c>
-      <c r="H15" s="15">
-        <f>H6/H5</f>
-        <v/>
-      </c>
-      <c r="I15" s="16">
-        <f>I6/I5</f>
         <v/>
       </c>
     </row>
@@ -969,16 +881,8 @@
         <f>F7/F6</f>
         <v/>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="16">
         <f>G7/G6</f>
-        <v/>
-      </c>
-      <c r="H16" s="15">
-        <f>H7/H6</f>
-        <v/>
-      </c>
-      <c r="I16" s="16">
-        <f>I7/I6</f>
         <v/>
       </c>
     </row>
@@ -1008,16 +912,8 @@
         <f>F8/F7</f>
         <v/>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="16">
         <f>G8/G7</f>
-        <v/>
-      </c>
-      <c r="H17" s="15">
-        <f>H8/H7</f>
-        <v/>
-      </c>
-      <c r="I17" s="16">
-        <f>I8/I7</f>
         <v/>
       </c>
     </row>
@@ -1047,16 +943,8 @@
         <f>F8/F6</f>
         <v/>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="16">
         <f>G8/G6</f>
-        <v/>
-      </c>
-      <c r="H18" s="15">
-        <f>H8/H6</f>
-        <v/>
-      </c>
-      <c r="I18" s="16">
-        <f>I8/I6</f>
         <v/>
       </c>
     </row>
@@ -1083,17 +971,11 @@
         <v>3390</v>
       </c>
       <c r="E21" s="18" t="n">
-        <v>3390</v>
+        <v>3051</v>
       </c>
       <c r="F21" s="18" t="n">
         <v>3390</v>
       </c>
-      <c r="G21" s="18" t="n">
-        <v>3051</v>
-      </c>
-      <c r="H21" s="18" t="n">
-        <v>3390</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1116,12 +998,6 @@
       <c r="F22" s="18" t="n">
         <v>851</v>
       </c>
-      <c r="G22" s="18" t="n">
-        <v>851</v>
-      </c>
-      <c r="H22" s="18" t="n">
-        <v>851</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1139,15 +1015,9 @@
         <v>1337</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>878</v>
+        <v>361</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>930</v>
-      </c>
-      <c r="G23" s="18" t="n">
-        <v>361</v>
-      </c>
-      <c r="H23" s="18" t="n">
         <v>368</v>
       </c>
     </row>
@@ -1167,15 +1037,9 @@
         <v>1202</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>1661</v>
+        <v>1839</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>1609</v>
-      </c>
-      <c r="G24" s="18" t="n">
-        <v>1839</v>
-      </c>
-      <c r="H24" s="18" t="n">
         <v>2171</v>
       </c>
     </row>
@@ -1195,19 +1059,13 @@
         <v>94920</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>183060</v>
+        <v>61020</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>152550</v>
-      </c>
-      <c r="G25" s="18" t="n">
-        <v>61020</v>
-      </c>
-      <c r="H25" s="18" t="n">
         <v>10170</v>
       </c>
-      <c r="I25" s="19">
-        <f>SUM(B25:H25)</f>
+      <c r="G25" s="19">
+        <f>SUM(B25:F25)</f>
         <v/>
       </c>
     </row>
@@ -1241,18 +1099,10 @@
         <f>G10/G25</f>
         <v/>
       </c>
-      <c r="H26" s="20">
-        <f>H10/H25</f>
-        <v/>
-      </c>
-      <c r="I26" s="20">
-        <f>I10/I25</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/кейс2_каналы_продаж/Кейс2_Анализ_каналов_продаж_заполнено.xlsx
+++ b/кейс2_каналы_продаж/Кейс2_Анализ_каналов_продаж_заполнено.xlsx
@@ -530,12 +530,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Блогер</t>
+          <t>Блогеры</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>канал n</t>
+          <t>ВК Канал (Таргет ВК)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>28000</v>
+        <v>26000</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>130000</v>
+        <v>120000</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>62000</v>
+        <v>6000</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>85000</v>
+        <v>80000</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>96000</v>
+        <v>100000</v>
       </c>
       <c r="G5" s="6">
         <f>SUM(B5:F5)</f>
@@ -577,19 +577,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>2100</v>
+        <v>260</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2480</v>
+        <v>1800</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>768</v>
+        <v>700</v>
       </c>
       <c r="G6" s="6">
         <f>SUM(B6:F6)</f>
@@ -603,19 +603,19 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>210</v>
+        <v>52</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>223</v>
+        <v>180</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>136</v>
+        <v>160</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G7" s="6">
         <f>SUM(B7:F7)</f>
@@ -629,19 +629,19 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>12</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>20</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G8" s="6">
         <f>SUM(B8:F8)</f>
@@ -655,19 +655,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>86840</v>
+        <v>28223</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>26052</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>33656</v>
+        <v>36060</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>36780</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>6513</v>
+        <v>12342</v>
       </c>
       <c r="G9" s="8">
         <f>SUM(B9:F9)</f>
@@ -681,19 +681,19 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>17000</v>
+        <v>5000</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>24000</v>
+        <v>12000</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>35000</v>
+        <v>15000</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="G10" s="8">
         <f>SUM(B10:F10)</f>
@@ -1002,7 +1002,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Комиссия канала + логистика + эквайринг на 1 заказ, ₽</t>
+          <t>Комиссия площадки + логистика + эквайринг на 1 заказ, ₽</t>
         </is>
       </c>
       <c r="B23" s="18" t="n">
@@ -1018,13 +1018,13 @@
         <v>361</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>368</v>
+        <v>776</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Маржа с 1 заказа, ₽</t>
+          <t>Маржа с 1 заказа, ₽ (= прибыль / продажи)</t>
         </is>
       </c>
       <c r="B24" s="18" t="n">
@@ -1040,7 +1040,7 @@
         <v>1839</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>2171</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="25">
@@ -1050,19 +1050,19 @@
         </is>
       </c>
       <c r="B25" s="18" t="n">
-        <v>135600</v>
+        <v>44070</v>
       </c>
       <c r="C25" s="18" t="n">
         <v>40680</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>94920</v>
+        <v>101700</v>
       </c>
       <c r="E25" s="18" t="n">
         <v>61020</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>10170</v>
+        <v>23730</v>
       </c>
       <c r="G25" s="19">
         <f>SUM(B25:F25)</f>

--- a/кейс2_каналы_продаж/Кейс2_Анализ_каналов_продаж_заполнено.xlsx
+++ b/кейс2_каналы_продаж/Кейс2_Анализ_каналов_продаж_заполнено.xlsx
@@ -557,7 +557,7 @@
         <v>120000</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>6000</v>
+        <v>60000</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>80000</v>
